--- a/extenbooks/S602.xlsx
+++ b/extenbooks/S602.xlsx
@@ -904,7 +904,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>calculated</t>
+          <t>book_period_validated</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S602.xlsx
+++ b/extenbooks/S602.xlsx
@@ -793,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -892,7 +892,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1952–2025</t>
+          <t>1952-1989</t>
         </is>
       </c>
     </row>
@@ -954,54 +954,55 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S602-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S602 — Social Insurance Tax Workers</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: 6 — The Net Social Wage</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>**Source Table**: Appendix Ch6 — `Table6_1_TaxAccounts.csv`, column `social_insurance_workers`</t>
+          <t># S602 — Social Insurance Tax Workers</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Units**: billions_usd</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Period**: 1952–1989 (book; S607 extends through 2024 via Table6_3_Extended)</t>
+          <t>**Chapter**: 6 — The Net Social Wage</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1010,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>**Content Type**: time_series</t>
+          <t>**Source Table**: Appendix Ch6 — `Table6_1_TaxAccounts.csv`, column `social_insurance_workers`</t>
         </is>
       </c>
     </row>
@@ -1017,31 +1018,39 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Status**: calculated</t>
+          <t>**Units**: billions_usd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>**Period**: 1952–1989 (book; S607 extends through 2024 via Table6_3_Extended)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Content Type**: time_series</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Worker share of social insurance contributions (FICA, Medicare).</t>
+          <t>## Definition</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1062,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>## Source</t>
+          <t>Worker share of social insurance contributions (FICA, Medicare).</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1074,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>`data/source/book_tables/Table6_1_TaxAccounts.csv` (digitized from book Appendix 6 tables). Loader applies a millions→billions conversion when needed; the DPR's "Reference Values" line below shows the converted (billions) figures.</t>
+          <t>## Source</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1086,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>## Construction</t>
+          <t>`data/source/book_tables/Table6_1_TaxAccounts.csv` (digitized from book Appendix 6 tables). Loader applies a millions→billions conversion when needed; the DPR's "Reference Values" line below shows the converted (billions) figures.</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1098,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pass-through loader: read column from the digitized book table, divide by 1000 to convert MILLIONS→BILLIONS for unit consistency with the registry's `units: billions_usd` field, write to intermediate + final stages.</t>
+          <t>## Construction</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1110,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>## Reference Values (Validation Benchmarks)</t>
+          <t>Pass-through loader: read column from the digitized book table, divide by 1000 to convert MILLIONS→BILLIONS for unit consistency with the registry's `units: billions_usd` field, write to intermediate + final stages.</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1122,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1952=6.92B; 1989=385.23B</t>
+          <t>## Reference Values (Validation Benchmarks)</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1134,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tolerance class: `dollar_series`. Validator script: `code/V03_validators/V03_S602_social_insurance_workers.py`. Both endpoints PASS.</t>
+          <t>1952=6.92B; 1989=385.23B</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1146,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>## Provenance Chain</t>
+          <t>Tolerance class: `dollar_series`. Validator script: `code/V03_validators/V03_S602_social_insurance_workers.py`. Both endpoints PASS.</t>
         </is>
       </c>
     </row>
@@ -1149,23 +1158,19 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>## Provenance Chain</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>data/source/book_tables/Table6_1_TaxAccounts.csv</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └── code/L01_loaders/L01_S602_social_insurance_workers.py</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1178,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └── data/intermediate/S602.csv</t>
+          <t>data/source/book_tables/Table6_1_TaxAccounts.csv</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1186,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">            └── code/P02_processors/P02_S602_social_insurance_workers.py</t>
+          <t xml:space="preserve">  └── code/L01_loaders/L01_S602_social_insurance_workers.py</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1194,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 └── data/final/S602.csv</t>
+          <t xml:space="preserve">       └── data/intermediate/S602.csv</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1202,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">                      └── code/V03_validators/V03_S602_social_insurance_workers.py</t>
+          <t xml:space="preserve">            └── code/P02_processors/P02_S602_social_insurance_workers.py</t>
         </is>
       </c>
     </row>
@@ -1205,19 +1210,23 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">                 └── data/final/S602.csv</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                      └── code/V03_validators/V03_S602_social_insurance_workers.py</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>## Citation</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1238,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Chapter 6 — The Net Social Wage. Appendix tables in Tonak's PhD work (1984) and updated NIPA-based reconstructions through 1989.</t>
+          <t>## Citation</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1250,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Chapter 6 — The Net Social Wage. Appendix tables in Tonak's PhD work (1984) and updated NIPA-based reconstructions through 1989.</t>
         </is>
       </c>
     </row>
@@ -1252,6 +1261,18 @@
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
         </is>
@@ -1268,12 +1289,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1296,179 +1317,278 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Social insurance contributions allocated to workers by identifying the worker share directly. Employee contributions to Social Security (OASDI) and Medicare (HI) are fully worker-borne. Employer contributions are treated as deferred worker compensation per classical political economy: the employer share is part of the cost of labor power and thus ultimately a worker burden.</t>
+          <t>As noted in Section 3.3, the nominal wages of production workers must be adjusted for the net transfers of royalties (ground rent, interest, and taxes) from variable capital. We calculate only the portion of this arising from the net transfer between workers and the state. The methodology and actual estimates are from Shaikh and Tonak (1987) for the United States from 1952 to 1985.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch6; CHAPTER_6_INVESTIGATION.md</t>
+          <t>ST_1994, Section 5.9, page 137; HDARP chunk_16 lines 69-73</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Total social insurance contributions from NIPA Table 3.1 (Government Current Receipts, social insurance contribution lines). Breakdown into employee vs employer shares from SSA and BEA supplementary tables. NIPA Table 3.1 provides federal social insurance receipts; state unemployment insurance from Table 3.3.</t>
+          <t>Group I - Social security taxes (100% from workers): Employee contributions; Employer contributions (deducted before workers receive income); Net government receipts from lotteries (treated as direct tax - footnote 1).</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BEA NIPA Tables 3.1, 3.3; SSA data</t>
+          <t>ST_1994, Appendix N (Tax Classification, Group I), page 357; HDARP chunk_38 lines 257-260</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>methodological_note</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Both employee and employer payroll contributions are attributed to workers, following the classical view that employer contributions represent a cost of employing labor that would otherwise be paid as wages. This is standard in the Shaikh-Tonak framework and differs from neoclassical incidence analysis which may split the burden.</t>
+          <t>Contributions for social insurance 1964: total 30.1, labor portion 30.1 (Direct, 100% from labor).</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ST_1994, Ch6; Shaikh_Tonak_1987</t>
+          <t>ST_1994, Table N.1 (Taxes, Group I), 1964 benchmark; HDARP chunk_38 line 300</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>empirical_finding</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Social insurance taxes grew substantially over the period 1952-1989, driven by rising OASDI rates (from 1.5% to 6.06% each for employee and employer) and expanding Medicare contributions after 1966. This made social insurance the second-largest tax component for workers after personal income tax.</t>
+          <t>Starting point: Total employee compensation (EC) - Cost to capitalists of hiring workers - Includes wages + employer contributions for social insurance + other labor income.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CHAPTER_6_INVESTIGATION.md</t>
+          <t>ST_1994, Appendix N preamble; HDARP chunk_38 lines 253-256</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cross_study_comparison</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>All three studies (AS2, Moos, Tonak) agree on social insurance allocation: both employee and employer contributions assigned to workers. This component shows the highest cross-study correlation because the allocation method is unambiguous.</t>
+          <t>Group I - Social security taxes (100% from workers): Employee contributions; Employer contributions (deducted before workers receive income); Net government receipts from lotteries (treated as direct tax - footnote 1).</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NSW_COMPARISON_REVIEW.md</t>
+          <t>ST_1994, Appendix N (Tax Classification, Group I); KB chunk_38 lines 257-260</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>decision_log_note</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DEC-008 (2026-04-09): Tax allocation methodology confirmed. The NRYwp net royalty framework (Section 3.3, pages 63-65) underpins the allocation of social insurance taxes to workers. Social insurance taxes are a direct royalty payment deducted from productive workers' wages. P09 methodology verified correct.</t>
+          <t>Starting point: Total employee compensation (EC) - Cost to capitalists of hiring workers - Includes wages + employer contributions for social insurance + other labor income.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NickyData/DECISION_LOG.md, DEC-008</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+          <t>ST_1994, Appendix N (Tax Classification preamble); KB chunk_38 lines 253-256</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Contributions for social insurance 1964: total 30.1, labor portion 30.1 (Direct, 100% from labor).</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.1 (Taxes, Group I); KB chunk_38 line 300</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Worker social insurance taxes include both employee and employer payroll contributions to OASDI, Medicare, and unemployment insurance. Both sides are attributed to workers per the classical political economy framework. DEC-008 confirms allocation method consistent with NRYwp net royalty framework.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>Tax rate (T1/EC): 1952: 0.18 (18%) -&gt; 1989: 0.32 (32%) - Increased 1.8x (workers paid more taxes).</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.2 trends 1952-89; KB chunk_38 lines 363-365</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Excluded taxes (not levied on workers - footnote 2): Corporate profit taxes; Indirect business taxes; Estate and gift taxes (only apply to highest income levels).</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N footnote 2; KB chunk_38 lines 268-271</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>methodology_description</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Social insurance contributions allocated to workers by identifying the worker share directly. Employee contributions to Social Security (OASDI) and Medicare (HI) are fully worker-borne. Employer contributions are treated as deferred worker compensation per classical political economy: the employer share is part of the cost of labor power and thus ultimately a worker burden.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch6; CHAPTER_6_INVESTIGATION.md</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Employer contribution incidence assumption differs from neoclassical analysis</t>
+          <t>Total social insurance contributions from NIPA Table 3.1 (Government Current Receipts, social insurance contribution lines). Breakdown into employee vs employer shares from SSA and BEA supplementary tables. NIPA Table 3.1 provides federal social insurance receipts; state unemployment insurance from Table 3.3.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BEA NIPA Tables 3.1, 3.3; SSA data</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>methodological_note</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Self-employment social insurance taxes require separate treatment</t>
+          <t>Both employee and employer payroll contributions are attributed to workers, following the classical view that employer contributions represent a cost of employing labor that would otherwise be paid as wages. This is standard in the Shaikh-Tonak framework and differs from neoclassical incidence analysis which may split the burden.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch6; Shaikh_Tonak_1987</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>empirical_finding</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Medicare tax base became uncapped in 1994, changing the distributional profile</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>Social insurance taxes grew substantially over the period 1952-1989, driven by rising OASDI rates (from 1.5% to 6.06% each for employee and employer) and expanding Medicare contributions after 1966. This made social insurance the second-largest tax component for workers after personal income tax.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CHAPTER_6_INVESTIGATION.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cross_study_comparison</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>All three studies (AS2, Moos, Tonak) agree on social insurance allocation: both employee and employer contributions assigned to workers. This component shows the highest cross-study correlation because the allocation method is unambiguous.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NSW_COMPARISON_REVIEW.md</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cross_references:</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>S601</t>
-        </is>
-      </c>
-    </row>
+          <t>decision_log_note</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>[internal-decision-record] (2026-04-09): Tax allocation methodology confirmed. The NRYwp net royalty framework (Section 3.3, pages 63-65) underpins the allocation of social insurance taxes to workers. Social insurance taxes are a direct royalty payment deducted from productive workers' wages. P09 methodology verified correct.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[internal-decision-log], [internal-decision-record]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>S603</t>
-        </is>
-      </c>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr"/>
+      <c r="C18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S604</t>
+          <t>Group I - Social security taxes (100% from workers): Employee contributions; Employer contributions (deducted before workers receive income); Net government receipts from lotteries (treated as direct tax - footnote 1).</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N (Tax Classification, Group I); KB chunk_38 lines 257-260</t>
         </is>
       </c>
     </row>
@@ -1476,49 +1596,178 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S607</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
+          <t>Starting point: Total employee compensation (EC) - Cost to capitalists of hiring workers - Includes wages + employer contributions for social insurance + other labor income.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N (Tax Classification preamble); KB chunk_38 lines 253-256</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Contributions for social insurance 1964: total 30.1, labor portion 30.1 (Direct, 100% from labor).</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.1 (Taxes, Group I); KB chunk_38 line 300</t>
+        </is>
+      </c>
+    </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>citations:</t>
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Tax rate (T1/EC): 1952: 0.18 (18%) -&gt; 1989: 0.32 (32%) - Increased 1.8x (workers paid more taxes).</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.2 trends 1952-89; KB chunk_38 lines 363-365</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>ST_1994</t>
-        </is>
-      </c>
+      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>BEA_NIPA</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Bureau of Economic Analysis. National Income and Product Accounts. https://apps.bea.gov/iTable/</t>
-        </is>
-      </c>
-    </row>
+          <t>Excluded taxes (not levied on workers - footnote 2): Corporate profit taxes; Indirect business taxes; Estate and gift taxes (only apply to highest income levels).</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N footnote 2; KB chunk_38 lines 268-271</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Worker social insurance taxes include both employee and employer payroll contributions to OASDI, Medicare, and unemployment insurance. Both sides are attributed to workers per the classical political economy framework. [internal-decision-record] confirms allocation method consistent with NRYwp net royalty framework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Employer contribution incidence assumption differs from neoclassical analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Self-employment social insurance taxes require separate treatment</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Medicare tax base became uncapped in 1994, changing the distributional profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>S601</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>S603</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>S604</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>S607</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BEA_NIPA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Bureau of Economic Analysis. National Income and Product Accounts. https://apps.bea.gov/iTable/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Shaikh_Tonak_1987</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1987. 'The Welfare State and the Myth of the Social Wage.' New School for Social Research working paper.</t>
         </is>
@@ -1535,7 +1784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1598,7 +1847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1868,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"1952": 6.923, "1989": 385.231}</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1892,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>level_series</t>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.0</t>
         </is>
       </c>
     </row>
